--- a/Advance Excel/Invoice.xlsx
+++ b/Advance Excel/Invoice.xlsx
@@ -2,12 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="33">
   <si>
     <t>Vansh Computer &amp; Acessories</t>
   </si>
@@ -71,12 +73,6 @@
     <t>Amount</t>
   </si>
   <si>
-    <t>Keyboard</t>
-  </si>
-  <si>
-    <t>Laptop</t>
-  </si>
-  <si>
     <t>Total Amount</t>
   </si>
   <si>
@@ -90,20 +86,71 @@
   </si>
   <si>
     <t>Authorised signature</t>
+  </si>
+  <si>
+    <t>22/4/26</t>
+  </si>
+  <si>
+    <t>Abhay</t>
+  </si>
+  <si>
+    <t>lucknow</t>
+  </si>
+  <si>
+    <t>Bill no</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>contact</t>
+  </si>
+  <si>
+    <t>address</t>
+  </si>
+  <si>
+    <t>total amount</t>
+  </si>
+  <si>
+    <t>cgst</t>
+  </si>
+  <si>
+    <t>sgst</t>
+  </si>
+  <si>
+    <t>grand total</t>
+  </si>
+  <si>
+    <t>Ayush</t>
+  </si>
+  <si>
+    <t>gdhdj</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="m/d/yyyy;@"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -513,6 +560,34 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color auto="1"/>
       </left>
@@ -559,21 +634,6 @@
     </border>
     <border>
       <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -618,19 +678,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -845,192 +892,216 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="18" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="3" fillId="4" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
@@ -1042,16 +1113,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1">
@@ -1118,7 +1189,151 @@
     <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="26">
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1312,25 +1527,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="15"/>
+      <tableStyleElement type="headerRow" dxfId="14"/>
+      <tableStyleElement type="totalRow" dxfId="13"/>
+      <tableStyleElement type="firstColumn" dxfId="12"/>
+      <tableStyleElement type="lastColumn" dxfId="11"/>
+      <tableStyleElement type="firstRowStripe" dxfId="10"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="9"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="25"/>
+      <tableStyleElement type="totalRow" dxfId="24"/>
+      <tableStyleElement type="firstRowStripe" dxfId="23"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="22"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="21"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="20"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="19"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="18"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="17"/>
+      <tableStyleElement type="pageFieldValues" dxfId="16"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -1339,6 +1554,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:I33" totalsRowShown="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:I33" etc:filterBottomFollowUsedRange="0"/>
+  <tableColumns count="9">
+    <tableColumn id="1" name="Bill no" dataDxfId="0"/>
+    <tableColumn id="2" name="date" dataDxfId="1"/>
+    <tableColumn id="3" name="name" dataDxfId="2"/>
+    <tableColumn id="4" name="contact" dataDxfId="3"/>
+    <tableColumn id="5" name="address" dataDxfId="4"/>
+    <tableColumn id="6" name="total amount" dataDxfId="5"/>
+    <tableColumn id="7" name="cgst" dataDxfId="6"/>
+    <tableColumn id="8" name="sgst" dataDxfId="7"/>
+    <tableColumn id="9" name="grand total" dataDxfId="8"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStylePreset3_Accent1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1591,406 +1824,427 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E43"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="2" max="2" width="14.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="13.5555555555556" customWidth="1"/>
     <col min="4" max="4" width="12.4444444444444" customWidth="1"/>
     <col min="5" max="5" width="31.4444444444444" customWidth="1"/>
+    <col min="8" max="8" width="11.7777777777778"/>
   </cols>
   <sheetData>
-    <row r="1" ht="21" spans="1:5">
-      <c r="A1" s="1" t="s">
+    <row r="1" ht="21" spans="1:8">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="3"/>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="8"/>
+      <c r="H1" s="9">
+        <f>B5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="11"/>
+      <c r="C2" s="11"/>
+      <c r="D2" s="11"/>
+      <c r="E2" s="12"/>
+      <c r="H2" s="9">
+        <f>E5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" ht="17.4" spans="1:5">
-      <c r="A4" s="10" t="s">
+      <c r="B3" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="15"/>
+      <c r="H3" s="9">
+        <f>B6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="17.4" spans="1:8">
+      <c r="A4" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="6"/>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="11" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="H4" s="9">
+        <f>C7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="14" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="15"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="11" t="s">
+      <c r="E5" s="21"/>
+      <c r="H5" s="9">
+        <f>C8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12"/>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="15"/>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="11" t="s">
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="23"/>
+      <c r="H6" s="9">
+        <f>E33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="15"/>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="11" t="s">
+      <c r="B7"/>
+      <c r="C7"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="23"/>
+      <c r="H7" s="9">
+        <f>E35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="15"/>
-    </row>
-    <row r="9" ht="17.4" spans="1:5">
-      <c r="A9" s="16" t="s">
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="23"/>
+      <c r="H8" s="9">
+        <f>E34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" ht="17.4" spans="1:8">
+      <c r="A9" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="26" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="19">
-        <v>1</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" s="20">
-        <v>50000</v>
-      </c>
-      <c r="D10" s="20">
-        <v>1</v>
-      </c>
-      <c r="E10" s="21">
+      <c r="H9" s="9">
+        <f>E36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="29" t="str">
         <f>IF(NOT(ISBLANK(B10)),(C10*D10),"")</f>
-        <v>50000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="19">
-        <v>2</v>
-      </c>
-      <c r="B11" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="20">
-        <v>450</v>
-      </c>
-      <c r="D11" s="20">
-        <v>7</v>
-      </c>
-      <c r="E11" s="21">
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="27"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="29" t="str">
         <f t="shared" ref="E11:E30" si="0">IF(NOT(ISBLANK(B11)),(C11*D11),"")</f>
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="19"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="21" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="27"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="19"/>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="21" t="str">
+    <row r="13" spans="1:8">
+      <c r="A13" s="27"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="21" t="str">
+    <row r="14" spans="1:8">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="28"/>
+      <c r="D14" s="28"/>
+      <c r="E14" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="19"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="21" t="str">
+    <row r="15" spans="1:8">
+      <c r="A15" s="27"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="28"/>
+      <c r="D15" s="28"/>
+      <c r="E15" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="21" t="str">
+    <row r="16" spans="1:8">
+      <c r="A16" s="27"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="19"/>
-      <c r="B17" s="20"/>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="21" t="str">
+      <c r="A17" s="27"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="19"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="21" t="str">
+      <c r="A18" s="27"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="19"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="20"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="21" t="str">
+      <c r="A19" s="27"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="19"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="21" t="str">
+      <c r="A20" s="27"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="19"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="21" t="str">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="19"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="20"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="21" t="str">
+      <c r="A22" s="27"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="19"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="20"/>
-      <c r="E23" s="21" t="str">
+      <c r="A23" s="27"/>
+      <c r="B23" s="28"/>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="19"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="21" t="str">
+      <c r="A24" s="27"/>
+      <c r="B24" s="28"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="19"/>
-      <c r="B25" s="20"/>
-      <c r="C25" s="20"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="21" t="str">
+      <c r="A25" s="27"/>
+      <c r="B25" s="28"/>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="19"/>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="21" t="str">
+      <c r="A26" s="27"/>
+      <c r="B26" s="28"/>
+      <c r="C26" s="28"/>
+      <c r="D26" s="28"/>
+      <c r="E26" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="19"/>
-      <c r="B27" s="20"/>
-      <c r="C27" s="20"/>
-      <c r="D27" s="20"/>
-      <c r="E27" s="21" t="str">
+      <c r="A27" s="27"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="19"/>
-      <c r="B28" s="20"/>
-      <c r="E28" s="21" t="str">
+      <c r="A28" s="27"/>
+      <c r="B28" s="28"/>
+      <c r="E28" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="19"/>
-      <c r="B29" s="20"/>
-      <c r="E29" s="21" t="str">
+      <c r="A29" s="27"/>
+      <c r="B29" s="28"/>
+      <c r="E29" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="19"/>
-      <c r="B30" s="20"/>
-      <c r="E30" s="21" t="str">
+      <c r="A30" s="27"/>
+      <c r="B30" s="28"/>
+      <c r="E30" s="29" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="19"/>
-      <c r="E31" s="21"/>
+      <c r="A31" s="27"/>
+      <c r="E31" s="29"/>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="19"/>
-      <c r="E32" s="21"/>
+      <c r="A32" s="27"/>
+      <c r="E32" s="29"/>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="19"/>
-      <c r="D33" s="22" t="s">
+      <c r="A33" s="27"/>
+      <c r="D33" s="30" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="31">
+        <f>IF(NOT(ISBLANK(E10)),SUM(E10:E30),"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="27"/>
+      <c r="D34" s="30" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="31">
+        <f>IF(NOT(ISBLANK(E10)),SUM(E10:E30)*0.09,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="27"/>
+      <c r="D35" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="E33" s="23">
-        <f>IF(NOT(ISBLANK(E10)),SUM(E10:E30),"")</f>
-        <v>53150</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="19"/>
-      <c r="D34" s="22" t="s">
+      <c r="E35" s="31">
+        <f>IF(NOT(ISBLANK(E10)),SUM(E10:E30)*0.09,"")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="27"/>
+      <c r="D36" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="E34" s="23">
-        <f>IF(NOT(ISBLANK(E10)),SUM(E10:E30)*0.09,"")</f>
-        <v>4783.5</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="19"/>
-      <c r="D35" s="22" t="s">
+      <c r="E36" s="33">
+        <f>SUM(E33:E35)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="27"/>
+      <c r="E37" s="29"/>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="27"/>
+      <c r="E38" s="29"/>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="27"/>
+      <c r="E39" s="29"/>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="27"/>
+      <c r="E40" s="29"/>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="27"/>
+      <c r="E41" s="29"/>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="27"/>
+      <c r="E42" s="29"/>
+    </row>
+    <row r="43" ht="15.15" spans="1:5">
+      <c r="A43" s="34"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="E35" s="23">
-        <f>IF(NOT(ISBLANK(E10)),SUM(E10:E30)*0.09,"")</f>
-        <v>4783.5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="19"/>
-      <c r="D36" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="25">
-        <f>SUM(E33:E35)</f>
-        <v>62717</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="19"/>
-      <c r="E37" s="21"/>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="19"/>
-      <c r="E38" s="21"/>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="19"/>
-      <c r="E39" s="21"/>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="19"/>
-      <c r="E40" s="21"/>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="19"/>
-      <c r="E41" s="21"/>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="19"/>
-      <c r="E42" s="21"/>
-    </row>
-    <row r="43" ht="15.15" spans="1:5">
-      <c r="A43" s="26"/>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="E43" s="29"/>
+      <c r="E43" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -2009,4 +2263,574 @@
   <pageSetup paperSize="1" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1">
+        <v>1009</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1">
+        <v>99846536</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1">
+        <v>23000</v>
+      </c>
+      <c r="G1">
+        <v>2070</v>
+      </c>
+      <c r="H1">
+        <v>2070</v>
+      </c>
+      <c r="I1">
+        <v>27140</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:J38"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="10.2222222222222"/>
+    <col min="4" max="4" width="11.7777777777778"/>
+    <col min="6" max="6" width="13.7777777777778" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:10">
+      <c r="A1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="3"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4">
+        <v>1232</v>
+      </c>
+      <c r="B4">
+        <v>46359</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4">
+        <v>8299356981</v>
+      </c>
+      <c r="E4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4">
+        <v>53150</v>
+      </c>
+      <c r="G4">
+        <v>4783.5</v>
+      </c>
+      <c r="H4">
+        <v>4783.5</v>
+      </c>
+      <c r="I4">
+        <v>62717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="4">
+        <v>1232</v>
+      </c>
+      <c r="B5" s="5">
+        <v>46359</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="4">
+        <v>8299356981</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5" s="4">
+        <v>53150</v>
+      </c>
+      <c r="G5" s="4">
+        <v>4783.5</v>
+      </c>
+      <c r="H5" s="4">
+        <v>4783.5</v>
+      </c>
+      <c r="I5" s="4">
+        <v>62717</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="1"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="1"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="1"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="1"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="1"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="1"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1"/>
+      <c r="C34" s="1"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="1"/>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="1"/>
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="1"/>
+      <c r="B38" s="1"/>
+      <c r="C38" s="1"/>
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>